--- a/6-DOF-Arm.xlsx
+++ b/6-DOF-Arm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erico\Documents\GitHub\6-DOF-Arm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan\Documents\6-DOF-Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A71F57B-C89F-4986-B8E2-5B735575E813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51FE0C9-5646-4EA1-A0B4-0A429005DA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Torque Budget" sheetId="1" r:id="rId1"/>
@@ -1544,7 +1544,6 @@
     <xf numFmtId="166" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1617,6 +1616,7 @@
     <xf numFmtId="166" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1911,9 +1911,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.85546875" customWidth="1"/>
+    <col min="1" max="1" width="45.88671875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -1923,30 +1923,30 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -2011,25 +2011,25 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>14</v>
@@ -2038,7 +2038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -2119,20 +2119,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="69" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>30</v>
       </c>
@@ -2154,20 +2154,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="69" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="93"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>47</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
@@ -2304,20 +2304,20 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="69" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-    </row>
-    <row r="37" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B36" s="93"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+    </row>
+    <row r="37" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>63</v>
       </c>
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B39" s="14">
         <f>B12</f>
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="D39" s="14">
         <f>B5</f>
@@ -2378,13 +2378,13 @@
       </c>
       <c r="F39" s="16">
         <f>B39*$B$21*D39</f>
-        <v>2.2072500000000002</v>
+        <v>2.182725</v>
       </c>
       <c r="G39" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>66</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>3.5316E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>67</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>2.0601000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>68</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>0.15107400000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>69</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>0.16186500000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>70</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>0.29430000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>71</v>
       </c>
@@ -2518,27 +2518,27 @@
       <c r="E45" s="18"/>
       <c r="F45" s="19">
         <f>SUM(F38:F44)</f>
-        <v>4.7833560000000004</v>
+        <v>4.7588310000000007</v>
       </c>
       <c r="G45" s="19">
         <f>SUM(G38:G44)</f>
         <v>0.66315600000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="69" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="69"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="93"/>
+      <c r="C47" s="93"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="93"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>5.8860000000000003E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>0.15696000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
         <v>75</v>
       </c>
@@ -2568,20 +2568,20 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="69" t="s">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="69"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="69"/>
-    </row>
-    <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="93"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="93"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93"/>
+    </row>
+    <row r="53" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>78</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>87</v>
       </c>
@@ -2646,17 +2646,17 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>88</v>
       </c>
       <c r="B55" s="16">
         <f>F45</f>
-        <v>4.7833560000000004</v>
+        <v>4.7588310000000007</v>
       </c>
       <c r="C55" s="16">
         <f t="shared" si="1"/>
-        <v>7.1750340000000001</v>
+        <v>7.138246500000001</v>
       </c>
       <c r="D55" s="24">
         <f>B30</f>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F55" s="16">
         <f t="shared" si="2"/>
-        <v>0.81532714688181274</v>
+        <v>0.81952899777277233</v>
       </c>
       <c r="G55" s="25" t="str">
         <f t="shared" si="3"/>
@@ -2683,7 +2683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>89</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>90</v>
       </c>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I57" s="13"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>91</v>
       </c>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="I58" s="13"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>92</v>
       </c>
@@ -2818,37 +2818,37 @@
       </c>
       <c r="I59" s="13"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>99</v>
       </c>
@@ -2882,7 +2882,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2892,17 +2892,17 @@
     <col min="6" max="6" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>102</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
         <v>108</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
         <v>114</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
         <v>120</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
         <v>126</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
         <v>132</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
         <v>138</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>144</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
         <v>150</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
         <v>156</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
         <v>162</v>
       </c>
@@ -3131,23 +3131,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C3DC63-880C-4C7A-BD99-15B2870A7881}">
   <dimension ref="A1:Q90"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="66.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>102</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
         <v>108</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>1333.81</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
         <v>207</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>1094.8399999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>205</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>203</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
         <v>201</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>199</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="34"/>
@@ -3387,7 +3387,7 @@
       <c r="J8" s="32"/>
       <c r="K8" s="32"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
         <v>197</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
         <v>256</v>
       </c>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P10" s="65"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>196</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>135.47999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="33" t="s">
         <v>194</v>
       </c>
@@ -3514,7 +3514,7 @@
       <c r="I12" s="33">
         <v>1</v>
       </c>
-      <c r="J12" s="70">
+      <c r="J12" s="69">
         <v>7.68</v>
       </c>
       <c r="K12" s="32">
@@ -3522,7 +3522,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="54"/>
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
@@ -3532,10 +3532,10 @@
       <c r="G13" s="54"/>
       <c r="H13" s="58"/>
       <c r="I13" s="54"/>
-      <c r="J13" s="92"/>
+      <c r="J13" s="91"/>
       <c r="K13" s="56"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
         <v>193</v>
       </c>
@@ -3563,13 +3563,13 @@
       <c r="I14" s="33">
         <v>3</v>
       </c>
-      <c r="J14" s="93"/>
+      <c r="J14" s="92"/>
       <c r="K14" s="32">
         <f>I14*E14</f>
         <v>38.97</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>192</v>
       </c>
@@ -3597,13 +3597,13 @@
       <c r="I15" s="33">
         <v>1</v>
       </c>
-      <c r="J15" s="93"/>
+      <c r="J15" s="92"/>
       <c r="K15" s="32">
         <f t="shared" ref="K15:K25" si="0">I15*E15</f>
         <v>9.99</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="33" t="s">
         <v>191</v>
       </c>
@@ -3631,13 +3631,13 @@
       <c r="I16" s="33">
         <v>1</v>
       </c>
-      <c r="J16" s="93"/>
+      <c r="J16" s="92"/>
       <c r="K16" s="32">
         <f t="shared" si="0"/>
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="54"/>
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
@@ -3647,10 +3647,10 @@
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
       <c r="I17" s="54"/>
-      <c r="J17" s="92"/>
+      <c r="J17" s="91"/>
       <c r="K17" s="56"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="33" t="s">
         <v>190</v>
       </c>
@@ -3678,13 +3678,13 @@
       <c r="I18" s="33">
         <v>1</v>
       </c>
-      <c r="J18" s="93"/>
+      <c r="J18" s="92"/>
       <c r="K18" s="32">
         <f t="shared" si="0"/>
         <v>6.99</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
         <v>189</v>
       </c>
@@ -3712,13 +3712,13 @@
       <c r="I19" s="33">
         <v>1</v>
       </c>
-      <c r="J19" s="93"/>
+      <c r="J19" s="92"/>
       <c r="K19" s="32">
         <f t="shared" si="0"/>
         <v>8.99</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="54"/>
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
@@ -3728,10 +3728,10 @@
       <c r="G20" s="54"/>
       <c r="H20" s="54"/>
       <c r="I20" s="54"/>
-      <c r="J20" s="92"/>
+      <c r="J20" s="91"/>
       <c r="K20" s="56"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="47" t="s">
         <v>188</v>
       </c>
@@ -3759,13 +3759,13 @@
       <c r="I21" s="33">
         <v>2</v>
       </c>
-      <c r="J21" s="93"/>
+      <c r="J21" s="92"/>
       <c r="K21" s="32">
         <f t="shared" si="0"/>
         <v>15.58</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
         <v>187</v>
       </c>
@@ -3778,28 +3778,28 @@
       <c r="D22" s="33">
         <v>9</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="69">
         <v>22.99</v>
       </c>
       <c r="F22" s="47" t="s">
         <v>247</v>
       </c>
-      <c r="G22" s="86" t="s">
+      <c r="G22" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="87">
         <v>46230</v>
       </c>
-      <c r="I22" s="90">
+      <c r="I22" s="89">
         <v>1</v>
       </c>
-      <c r="J22" s="93"/>
-      <c r="K22" s="70">
+      <c r="J22" s="92"/>
+      <c r="K22" s="69">
         <f t="shared" si="0"/>
         <v>22.99</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>186</v>
       </c>
@@ -3812,17 +3812,17 @@
       <c r="D23" s="33">
         <v>7</v>
       </c>
-      <c r="E23" s="71"/>
+      <c r="E23" s="70"/>
       <c r="F23" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="G23" s="87"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="71"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G23" s="86"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="70"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>185</v>
       </c>
@@ -3844,10 +3844,10 @@
         <v>248</v>
       </c>
       <c r="I24" s="33"/>
-      <c r="J24" s="93"/>
+      <c r="J24" s="92"/>
       <c r="K24" s="32"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
         <v>218</v>
       </c>
@@ -3875,13 +3875,13 @@
       <c r="I25" s="33">
         <v>1</v>
       </c>
-      <c r="J25" s="93"/>
+      <c r="J25" s="92"/>
       <c r="K25" s="32">
         <f t="shared" si="0"/>
         <v>7.29</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
         <v>219</v>
       </c>
@@ -3907,10 +3907,10 @@
         <v>248</v>
       </c>
       <c r="I26" s="33"/>
-      <c r="J26" s="71"/>
+      <c r="J26" s="70"/>
       <c r="K26" s="32"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="54"/>
       <c r="B27" s="54"/>
       <c r="C27" s="55"/>
@@ -3923,7 +3923,7 @@
       <c r="J27" s="56"/>
       <c r="K27" s="56"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="33" t="s">
         <v>220</v>
       </c>
@@ -3937,16 +3937,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="32"/>
-      <c r="F28" s="72" t="s">
+      <c r="F28" s="71" t="s">
         <v>233</v>
       </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="74"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="33" t="s">
         <v>222</v>
       </c>
@@ -3960,14 +3960,14 @@
         <v>1</v>
       </c>
       <c r="E29" s="32"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="76"/>
-      <c r="K29" s="77"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="76"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="33" t="s">
         <v>223</v>
       </c>
@@ -3981,14 +3981,14 @@
         <v>78</v>
       </c>
       <c r="E30" s="32"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="77"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="76"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>224</v>
       </c>
@@ -4002,14 +4002,14 @@
         <v>39</v>
       </c>
       <c r="E31" s="32"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="77"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="76"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>225</v>
       </c>
@@ -4023,14 +4023,14 @@
         <v>2</v>
       </c>
       <c r="E32" s="32"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="77"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="76"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>226</v>
       </c>
@@ -4044,14 +4044,14 @@
         <v>2</v>
       </c>
       <c r="E33" s="32"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="77"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="76"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>227</v>
       </c>
@@ -4065,14 +4065,14 @@
         <v>1</v>
       </c>
       <c r="E34" s="32"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="77"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="76"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>228</v>
       </c>
@@ -4086,14 +4086,14 @@
         <v>1</v>
       </c>
       <c r="E35" s="32"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="77"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F35" s="74"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="75"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="76"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>229</v>
       </c>
@@ -4107,14 +4107,14 @@
         <v>1</v>
       </c>
       <c r="E36" s="32"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="77"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F36" s="74"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="76"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="33" t="s">
         <v>231</v>
       </c>
@@ -4128,15 +4128,15 @@
         <v>1</v>
       </c>
       <c r="E37" s="32"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="77"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="76"/>
       <c r="Q37" s="48"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>232</v>
       </c>
@@ -4150,14 +4150,14 @@
         <v>1</v>
       </c>
       <c r="E38" s="32"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="77"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F38" s="74"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="76"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="33" t="s">
         <v>244</v>
       </c>
@@ -4171,14 +4171,14 @@
         <v>1</v>
       </c>
       <c r="E39" s="32"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="77"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F39" s="74"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="76"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>245</v>
       </c>
@@ -4192,14 +4192,14 @@
         <v>1</v>
       </c>
       <c r="E40" s="32"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="80"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F40" s="77"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="79"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="36">
         <v>1.3</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>103.49</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>184</v>
       </c>
@@ -4253,7 +4253,7 @@
       <c r="I42" s="33">
         <v>1</v>
       </c>
-      <c r="J42" s="82">
+      <c r="J42" s="81">
         <v>5.87</v>
       </c>
       <c r="K42" s="32">
@@ -4261,7 +4261,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="54"/>
       <c r="B43" s="54"/>
       <c r="C43" s="55"/>
@@ -4271,10 +4271,10 @@
       <c r="G43" s="54"/>
       <c r="H43" s="58"/>
       <c r="I43" s="54"/>
-      <c r="J43" s="83"/>
+      <c r="J43" s="82"/>
       <c r="K43" s="56"/>
     </row>
-    <row r="44" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
         <v>182</v>
       </c>
@@ -4302,13 +4302,13 @@
       <c r="I44" s="33">
         <v>3</v>
       </c>
-      <c r="J44" s="84"/>
+      <c r="J44" s="83"/>
       <c r="K44" s="32">
         <f>I44*E44</f>
         <v>38.97</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
         <v>179</v>
       </c>
@@ -4336,13 +4336,13 @@
       <c r="I45" s="33">
         <v>1</v>
       </c>
-      <c r="J45" s="84"/>
+      <c r="J45" s="83"/>
       <c r="K45" s="32">
         <f t="shared" ref="K45:K46" si="1">I45*E45</f>
         <v>8.09</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
         <v>291</v>
       </c>
@@ -4370,13 +4370,13 @@
       <c r="I46" s="33">
         <v>1</v>
       </c>
-      <c r="J46" s="84"/>
+      <c r="J46" s="83"/>
       <c r="K46" s="32">
         <f t="shared" si="1"/>
         <v>9.99</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="54"/>
       <c r="B47" s="54"/>
       <c r="C47" s="55"/>
@@ -4386,10 +4386,10 @@
       <c r="G47" s="54"/>
       <c r="H47" s="54"/>
       <c r="I47" s="54"/>
-      <c r="J47" s="83"/>
+      <c r="J47" s="82"/>
       <c r="K47" s="56"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="47" t="s">
         <v>292</v>
       </c>
@@ -4415,13 +4415,13 @@
         <v>259</v>
       </c>
       <c r="I48" s="33"/>
-      <c r="J48" s="84"/>
+      <c r="J48" s="83"/>
       <c r="K48" s="32">
         <f t="shared" ref="K48:K55" si="2">I48*E48</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="47" t="s">
         <v>293</v>
       </c>
@@ -4447,13 +4447,13 @@
         <v>259</v>
       </c>
       <c r="I49" s="33"/>
-      <c r="J49" s="84"/>
+      <c r="J49" s="83"/>
       <c r="K49" s="32">
         <f>I49*E49</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="59"/>
       <c r="B50" s="54"/>
       <c r="C50" s="55"/>
@@ -4463,10 +4463,10 @@
       <c r="G50" s="54"/>
       <c r="H50" s="54"/>
       <c r="I50" s="54"/>
-      <c r="J50" s="83"/>
+      <c r="J50" s="82"/>
       <c r="K50" s="56"/>
     </row>
-    <row r="51" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="47" t="s">
         <v>294</v>
       </c>
@@ -4494,14 +4494,14 @@
       <c r="I51" s="33">
         <v>3</v>
       </c>
-      <c r="J51" s="84"/>
+      <c r="J51" s="83"/>
       <c r="K51" s="32">
         <f t="shared" ref="K51:K52" si="3">I51*E51</f>
         <v>23.37</v>
       </c>
       <c r="Q51" s="31"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
         <v>295</v>
       </c>
@@ -4514,26 +4514,26 @@
       <c r="D52" s="33">
         <v>9</v>
       </c>
-      <c r="E52" s="70">
+      <c r="E52" s="69">
         <v>22.99</v>
       </c>
       <c r="F52" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="G52" s="86" t="s">
+      <c r="G52" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="88" t="s">
+      <c r="H52" s="87" t="s">
         <v>259</v>
       </c>
-      <c r="I52" s="90"/>
-      <c r="J52" s="84"/>
-      <c r="K52" s="70">
+      <c r="I52" s="89"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
         <v>296</v>
       </c>
@@ -4546,17 +4546,17 @@
       <c r="D53" s="33">
         <v>7</v>
       </c>
-      <c r="E53" s="71"/>
+      <c r="E53" s="70"/>
       <c r="F53" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="G53" s="87"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="91"/>
-      <c r="J53" s="84"/>
-      <c r="K53" s="71"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G53" s="86"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="70"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="47" t="s">
         <v>297</v>
       </c>
@@ -4584,13 +4584,13 @@
       <c r="I54" s="33">
         <v>1</v>
       </c>
-      <c r="J54" s="84"/>
+      <c r="J54" s="83"/>
       <c r="K54" s="32">
         <f>I54*E54</f>
         <v>9.99</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="47" t="s">
         <v>298</v>
       </c>
@@ -4616,13 +4616,13 @@
         <v>258</v>
       </c>
       <c r="I55" s="47"/>
-      <c r="J55" s="84"/>
+      <c r="J55" s="83"/>
       <c r="K55" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="47" t="s">
         <v>299</v>
       </c>
@@ -4648,10 +4648,10 @@
         <v>248</v>
       </c>
       <c r="I56" s="33"/>
-      <c r="J56" s="85"/>
+      <c r="J56" s="84"/>
       <c r="K56" s="32"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="54"/>
       <c r="B57" s="54"/>
       <c r="C57" s="55"/>
@@ -4664,7 +4664,7 @@
       <c r="J57" s="56"/>
       <c r="K57" s="56"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="47" t="s">
         <v>300</v>
       </c>
@@ -4678,16 +4678,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="32"/>
-      <c r="F58" s="81" t="s">
+      <c r="F58" s="80" t="s">
         <v>290</v>
       </c>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="73"/>
-      <c r="K58" s="74"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G58" s="72"/>
+      <c r="H58" s="72"/>
+      <c r="I58" s="72"/>
+      <c r="J58" s="72"/>
+      <c r="K58" s="73"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="47" t="s">
         <v>301</v>
       </c>
@@ -4701,14 +4701,14 @@
         <v>1</v>
       </c>
       <c r="E59" s="32"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="76"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="76"/>
-      <c r="J59" s="76"/>
-      <c r="K59" s="77"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F59" s="74"/>
+      <c r="G59" s="75"/>
+      <c r="H59" s="75"/>
+      <c r="I59" s="75"/>
+      <c r="J59" s="75"/>
+      <c r="K59" s="76"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="47" t="s">
         <v>302</v>
       </c>
@@ -4722,14 +4722,14 @@
         <v>44</v>
       </c>
       <c r="E60" s="32"/>
-      <c r="F60" s="75"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="77"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F60" s="74"/>
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="75"/>
+      <c r="J60" s="75"/>
+      <c r="K60" s="76"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="47" t="s">
         <v>303</v>
       </c>
@@ -4743,14 +4743,14 @@
         <v>22</v>
       </c>
       <c r="E61" s="32"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="76"/>
-      <c r="J61" s="76"/>
-      <c r="K61" s="77"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F61" s="74"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="75"/>
+      <c r="J61" s="75"/>
+      <c r="K61" s="76"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="47" t="s">
         <v>304</v>
       </c>
@@ -4764,14 +4764,14 @@
         <v>2</v>
       </c>
       <c r="E62" s="32"/>
-      <c r="F62" s="75"/>
-      <c r="G62" s="76"/>
-      <c r="H62" s="76"/>
-      <c r="I62" s="76"/>
-      <c r="J62" s="76"/>
-      <c r="K62" s="77"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F62" s="74"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="75"/>
+      <c r="I62" s="75"/>
+      <c r="J62" s="75"/>
+      <c r="K62" s="76"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="47" t="s">
         <v>305</v>
       </c>
@@ -4785,14 +4785,14 @@
         <v>2</v>
       </c>
       <c r="E63" s="32"/>
-      <c r="F63" s="75"/>
-      <c r="G63" s="76"/>
-      <c r="H63" s="76"/>
-      <c r="I63" s="76"/>
-      <c r="J63" s="76"/>
-      <c r="K63" s="77"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F63" s="74"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="75"/>
+      <c r="I63" s="75"/>
+      <c r="J63" s="75"/>
+      <c r="K63" s="76"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="47" t="s">
         <v>306</v>
       </c>
@@ -4806,14 +4806,14 @@
         <v>1</v>
       </c>
       <c r="E64" s="32"/>
-      <c r="F64" s="75"/>
-      <c r="G64" s="76"/>
-      <c r="H64" s="76"/>
-      <c r="I64" s="76"/>
-      <c r="J64" s="76"/>
-      <c r="K64" s="77"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F64" s="74"/>
+      <c r="G64" s="75"/>
+      <c r="H64" s="75"/>
+      <c r="I64" s="75"/>
+      <c r="J64" s="75"/>
+      <c r="K64" s="76"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="47" t="s">
         <v>307</v>
       </c>
@@ -4827,14 +4827,14 @@
         <v>1</v>
       </c>
       <c r="E65" s="32"/>
-      <c r="F65" s="75"/>
-      <c r="G65" s="76"/>
-      <c r="H65" s="76"/>
-      <c r="I65" s="76"/>
-      <c r="J65" s="76"/>
-      <c r="K65" s="77"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F65" s="74"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="75"/>
+      <c r="J65" s="75"/>
+      <c r="K65" s="76"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="47" t="s">
         <v>308</v>
       </c>
@@ -4848,14 +4848,14 @@
         <v>1</v>
       </c>
       <c r="E66" s="32"/>
-      <c r="F66" s="75"/>
-      <c r="G66" s="76"/>
-      <c r="H66" s="76"/>
-      <c r="I66" s="76"/>
-      <c r="J66" s="76"/>
-      <c r="K66" s="77"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F66" s="74"/>
+      <c r="G66" s="75"/>
+      <c r="H66" s="75"/>
+      <c r="I66" s="75"/>
+      <c r="J66" s="75"/>
+      <c r="K66" s="76"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="47" t="s">
         <v>309</v>
       </c>
@@ -4869,14 +4869,14 @@
         <v>1</v>
       </c>
       <c r="E67" s="32"/>
-      <c r="F67" s="75"/>
-      <c r="G67" s="76"/>
-      <c r="H67" s="76"/>
-      <c r="I67" s="76"/>
-      <c r="J67" s="76"/>
-      <c r="K67" s="77"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F67" s="74"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="75"/>
+      <c r="I67" s="75"/>
+      <c r="J67" s="75"/>
+      <c r="K67" s="76"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="47" t="s">
         <v>310</v>
       </c>
@@ -4890,14 +4890,14 @@
         <v>1</v>
       </c>
       <c r="E68" s="32"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="76"/>
-      <c r="H68" s="76"/>
-      <c r="I68" s="76"/>
-      <c r="J68" s="76"/>
-      <c r="K68" s="77"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F68" s="74"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="75"/>
+      <c r="I68" s="75"/>
+      <c r="J68" s="75"/>
+      <c r="K68" s="76"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="47" t="s">
         <v>311</v>
       </c>
@@ -4911,14 +4911,14 @@
         <v>1</v>
       </c>
       <c r="E69" s="32"/>
-      <c r="F69" s="75"/>
-      <c r="G69" s="76"/>
-      <c r="H69" s="76"/>
-      <c r="I69" s="76"/>
-      <c r="J69" s="76"/>
-      <c r="K69" s="77"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F69" s="74"/>
+      <c r="G69" s="75"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="75"/>
+      <c r="J69" s="75"/>
+      <c r="K69" s="76"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="47" t="s">
         <v>312</v>
       </c>
@@ -4932,14 +4932,14 @@
         <v>1</v>
       </c>
       <c r="E70" s="32"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="76"/>
-      <c r="H70" s="76"/>
-      <c r="I70" s="76"/>
-      <c r="J70" s="76"/>
-      <c r="K70" s="77"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="75"/>
+      <c r="I70" s="75"/>
+      <c r="J70" s="75"/>
+      <c r="K70" s="76"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="47" t="s">
         <v>312</v>
       </c>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="E71" s="32"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="36">
         <v>1.4</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>60.139999999999993</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="47" t="s">
         <v>184</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="54"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
@@ -5025,7 +5025,7 @@
       <c r="J75" s="67"/>
       <c r="K75" s="56"/>
     </row>
-    <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="47" t="s">
         <v>182</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>38.97</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="47" t="s">
         <v>179</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="47"/>
       <c r="B78" s="33"/>
       <c r="C78" s="34"/>
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="E22:E23"/>

--- a/6-DOF-Arm.xlsx
+++ b/6-DOF-Arm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan\Documents\6-DOF-Arm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erico\Documents\GitHub\6-DOF-Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51FE0C9-5646-4EA1-A0B4-0A429005DA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="30690" windowHeight="18270" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Torque Budget" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="BOM" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1544,6 +1545,7 @@
     <xf numFmtId="166" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1616,7 +1618,6 @@
     <xf numFmtId="166" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1911,9 +1912,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.88671875" customWidth="1"/>
+    <col min="1" max="1" width="45.85546875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -1923,30 +1924,30 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="93" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1968,7 +1969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1982,7 +1983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +1997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -2011,20 +2012,20 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="93" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -2052,7 +2053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -2080,7 +2081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -2094,7 +2095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -2105,7 +2106,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -2119,20 +2120,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
@@ -2143,7 +2144,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>30</v>
       </c>
@@ -2154,20 +2155,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="93" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
@@ -2181,7 +2182,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
@@ -2195,7 +2196,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -2209,7 +2210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -2237,7 +2238,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>47</v>
       </c>
@@ -2251,7 +2252,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
@@ -2265,7 +2266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
@@ -2293,7 +2294,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
@@ -2304,20 +2305,20 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="93" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="93"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-    </row>
-    <row r="37" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+    </row>
+    <row r="37" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>63</v>
       </c>
@@ -2361,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>65</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>66</v>
       </c>
@@ -2409,7 +2410,7 @@
         <v>3.5316E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>67</v>
       </c>
@@ -2434,7 +2435,7 @@
         <v>2.0601000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>68</v>
       </c>
@@ -2459,7 +2460,7 @@
         <v>0.15107400000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>69</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>0.16186500000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>70</v>
       </c>
@@ -2509,7 +2510,7 @@
         <v>0.29430000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>71</v>
       </c>
@@ -2525,20 +2526,20 @@
         <v>0.66315600000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="93" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="93"/>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
-      <c r="F47" s="93"/>
-      <c r="G47" s="93"/>
-      <c r="H47" s="93"/>
-      <c r="I47" s="93"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B47" s="69"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
@@ -2547,7 +2548,7 @@
         <v>5.8860000000000003E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
@@ -2556,7 +2557,7 @@
         <v>0.15696000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>75</v>
       </c>
@@ -2568,20 +2569,20 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="93" t="s">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="93"/>
-      <c r="C52" s="93"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="93"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="93"/>
-      <c r="H52" s="93"/>
-      <c r="I52" s="93"/>
-    </row>
-    <row r="53" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B52" s="69"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="69"/>
+    </row>
+    <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>78</v>
       </c>
@@ -2610,7 +2611,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>87</v>
       </c>
@@ -2646,7 +2647,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>88</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>89</v>
       </c>
@@ -2720,7 +2721,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>90</v>
       </c>
@@ -2753,7 +2754,7 @@
       </c>
       <c r="I57" s="13"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>91</v>
       </c>
@@ -2786,7 +2787,7 @@
       </c>
       <c r="I58" s="13"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>92</v>
       </c>
@@ -2818,37 +2819,37 @@
       </c>
       <c r="I59" s="13"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>99</v>
       </c>
@@ -2882,7 +2883,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2892,17 +2893,17 @@
     <col min="6" max="6" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>102</v>
       </c>
@@ -2922,7 +2923,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>108</v>
       </c>
@@ -2942,7 +2943,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>114</v>
       </c>
@@ -2962,7 +2963,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>120</v>
       </c>
@@ -2982,7 +2983,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>126</v>
       </c>
@@ -3002,7 +3003,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>132</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>138</v>
       </c>
@@ -3042,7 +3043,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>144</v>
       </c>
@@ -3062,7 +3063,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>150</v>
       </c>
@@ -3082,7 +3083,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>156</v>
       </c>
@@ -3102,7 +3103,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>162</v>
       </c>
@@ -3131,23 +3132,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C3DC63-880C-4C7A-BD99-15B2870A7881}">
   <dimension ref="A1:Q90"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="66.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>102</v>
       </c>
@@ -3182,7 +3183,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
         <v>108</v>
       </c>
@@ -3208,7 +3209,7 @@
         <v>1333.81</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
         <v>207</v>
       </c>
@@ -3230,7 +3231,7 @@
         <v>1094.8399999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>205</v>
       </c>
@@ -3266,7 +3267,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>203</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>201</v>
       </c>
@@ -3338,7 +3339,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>199</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="34"/>
@@ -3387,7 +3388,7 @@
       <c r="J8" s="32"/>
       <c r="K8" s="32"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>197</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>256</v>
       </c>
@@ -3460,7 +3461,7 @@
       </c>
       <c r="P10" s="65"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
         <v>196</v>
       </c>
@@ -3486,7 +3487,7 @@
         <v>135.47999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>194</v>
       </c>
@@ -3514,7 +3515,7 @@
       <c r="I12" s="33">
         <v>1</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="70">
         <v>7.68</v>
       </c>
       <c r="K12" s="32">
@@ -3522,7 +3523,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="54"/>
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
@@ -3532,10 +3533,10 @@
       <c r="G13" s="54"/>
       <c r="H13" s="58"/>
       <c r="I13" s="54"/>
-      <c r="J13" s="91"/>
+      <c r="J13" s="92"/>
       <c r="K13" s="56"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>193</v>
       </c>
@@ -3563,13 +3564,13 @@
       <c r="I14" s="33">
         <v>3</v>
       </c>
-      <c r="J14" s="92"/>
+      <c r="J14" s="93"/>
       <c r="K14" s="32">
         <f>I14*E14</f>
         <v>38.97</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>192</v>
       </c>
@@ -3597,13 +3598,13 @@
       <c r="I15" s="33">
         <v>1</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="93"/>
       <c r="K15" s="32">
         <f t="shared" ref="K15:K25" si="0">I15*E15</f>
         <v>9.99</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>191</v>
       </c>
@@ -3631,13 +3632,13 @@
       <c r="I16" s="33">
         <v>1</v>
       </c>
-      <c r="J16" s="92"/>
+      <c r="J16" s="93"/>
       <c r="K16" s="32">
         <f t="shared" si="0"/>
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="54"/>
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
@@ -3647,10 +3648,10 @@
       <c r="G17" s="54"/>
       <c r="H17" s="54"/>
       <c r="I17" s="54"/>
-      <c r="J17" s="91"/>
+      <c r="J17" s="92"/>
       <c r="K17" s="56"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>190</v>
       </c>
@@ -3678,13 +3679,13 @@
       <c r="I18" s="33">
         <v>1</v>
       </c>
-      <c r="J18" s="92"/>
+      <c r="J18" s="93"/>
       <c r="K18" s="32">
         <f t="shared" si="0"/>
         <v>6.99</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>189</v>
       </c>
@@ -3712,13 +3713,13 @@
       <c r="I19" s="33">
         <v>1</v>
       </c>
-      <c r="J19" s="92"/>
+      <c r="J19" s="93"/>
       <c r="K19" s="32">
         <f t="shared" si="0"/>
         <v>8.99</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="54"/>
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
@@ -3728,10 +3729,10 @@
       <c r="G20" s="54"/>
       <c r="H20" s="54"/>
       <c r="I20" s="54"/>
-      <c r="J20" s="91"/>
+      <c r="J20" s="92"/>
       <c r="K20" s="56"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="47" t="s">
         <v>188</v>
       </c>
@@ -3759,13 +3760,13 @@
       <c r="I21" s="33">
         <v>2</v>
       </c>
-      <c r="J21" s="92"/>
+      <c r="J21" s="93"/>
       <c r="K21" s="32">
         <f t="shared" si="0"/>
         <v>15.58</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="47" t="s">
         <v>187</v>
       </c>
@@ -3778,28 +3779,28 @@
       <c r="D22" s="33">
         <v>9</v>
       </c>
-      <c r="E22" s="69">
+      <c r="E22" s="70">
         <v>22.99</v>
       </c>
       <c r="F22" s="47" t="s">
         <v>247</v>
       </c>
-      <c r="G22" s="85" t="s">
+      <c r="G22" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="H22" s="87">
+      <c r="H22" s="88">
         <v>46230</v>
       </c>
-      <c r="I22" s="89">
+      <c r="I22" s="90">
         <v>1</v>
       </c>
-      <c r="J22" s="92"/>
-      <c r="K22" s="69">
+      <c r="J22" s="93"/>
+      <c r="K22" s="70">
         <f t="shared" si="0"/>
         <v>22.99</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="s">
         <v>186</v>
       </c>
@@ -3812,17 +3813,17 @@
       <c r="D23" s="33">
         <v>7</v>
       </c>
-      <c r="E23" s="70"/>
+      <c r="E23" s="71"/>
       <c r="F23" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="G23" s="86"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="70"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G23" s="87"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="71"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="s">
         <v>185</v>
       </c>
@@ -3844,10 +3845,10 @@
         <v>248</v>
       </c>
       <c r="I24" s="33"/>
-      <c r="J24" s="92"/>
+      <c r="J24" s="93"/>
       <c r="K24" s="32"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="47" t="s">
         <v>218</v>
       </c>
@@ -3875,13 +3876,13 @@
       <c r="I25" s="33">
         <v>1</v>
       </c>
-      <c r="J25" s="92"/>
+      <c r="J25" s="93"/>
       <c r="K25" s="32">
         <f t="shared" si="0"/>
         <v>7.29</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="47" t="s">
         <v>219</v>
       </c>
@@ -3907,10 +3908,10 @@
         <v>248</v>
       </c>
       <c r="I26" s="33"/>
-      <c r="J26" s="70"/>
+      <c r="J26" s="71"/>
       <c r="K26" s="32"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="54"/>
       <c r="B27" s="54"/>
       <c r="C27" s="55"/>
@@ -3923,7 +3924,7 @@
       <c r="J27" s="56"/>
       <c r="K27" s="56"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>220</v>
       </c>
@@ -3937,16 +3938,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="32"/>
-      <c r="F28" s="71" t="s">
+      <c r="F28" s="72" t="s">
         <v>233</v>
       </c>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="73"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="74"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
         <v>222</v>
       </c>
@@ -3960,14 +3961,14 @@
         <v>1</v>
       </c>
       <c r="E29" s="32"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="76"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F29" s="75"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="76"/>
+      <c r="K29" s="77"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="33" t="s">
         <v>223</v>
       </c>
@@ -3981,14 +3982,14 @@
         <v>78</v>
       </c>
       <c r="E30" s="32"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="76"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F30" s="75"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="77"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="33" t="s">
         <v>224</v>
       </c>
@@ -4002,14 +4003,14 @@
         <v>39</v>
       </c>
       <c r="E31" s="32"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="76"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F31" s="75"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="77"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
         <v>225</v>
       </c>
@@ -4023,14 +4024,14 @@
         <v>2</v>
       </c>
       <c r="E32" s="32"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="76"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F32" s="75"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="77"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>226</v>
       </c>
@@ -4044,14 +4045,14 @@
         <v>2</v>
       </c>
       <c r="E33" s="32"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="76"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="77"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
         <v>227</v>
       </c>
@@ -4065,14 +4066,14 @@
         <v>1</v>
       </c>
       <c r="E34" s="32"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="76"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F34" s="75"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="77"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
         <v>228</v>
       </c>
@@ -4086,14 +4087,14 @@
         <v>1</v>
       </c>
       <c r="E35" s="32"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="76"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F35" s="75"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="77"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
         <v>229</v>
       </c>
@@ -4107,14 +4108,14 @@
         <v>1</v>
       </c>
       <c r="E36" s="32"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="76"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F36" s="75"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="77"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
         <v>231</v>
       </c>
@@ -4128,15 +4129,15 @@
         <v>1</v>
       </c>
       <c r="E37" s="32"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="76"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="77"/>
       <c r="Q37" s="48"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="33" t="s">
         <v>232</v>
       </c>
@@ -4150,14 +4151,14 @@
         <v>1</v>
       </c>
       <c r="E38" s="32"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="76"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F38" s="75"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="77"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="33" t="s">
         <v>244</v>
       </c>
@@ -4171,14 +4172,14 @@
         <v>1</v>
       </c>
       <c r="E39" s="32"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="76"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F39" s="75"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="77"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
         <v>245</v>
       </c>
@@ -4192,14 +4193,14 @@
         <v>1</v>
       </c>
       <c r="E40" s="32"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="79"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F40" s="78"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="80"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="36">
         <v>1.3</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>103.49</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
         <v>184</v>
       </c>
@@ -4253,7 +4254,7 @@
       <c r="I42" s="33">
         <v>1</v>
       </c>
-      <c r="J42" s="81">
+      <c r="J42" s="82">
         <v>5.87</v>
       </c>
       <c r="K42" s="32">
@@ -4261,7 +4262,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="54"/>
       <c r="B43" s="54"/>
       <c r="C43" s="55"/>
@@ -4271,10 +4272,10 @@
       <c r="G43" s="54"/>
       <c r="H43" s="58"/>
       <c r="I43" s="54"/>
-      <c r="J43" s="82"/>
+      <c r="J43" s="83"/>
       <c r="K43" s="56"/>
     </row>
-    <row r="44" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="47" t="s">
         <v>182</v>
       </c>
@@ -4302,13 +4303,13 @@
       <c r="I44" s="33">
         <v>3</v>
       </c>
-      <c r="J44" s="83"/>
+      <c r="J44" s="84"/>
       <c r="K44" s="32">
         <f>I44*E44</f>
         <v>38.97</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="47" t="s">
         <v>179</v>
       </c>
@@ -4336,13 +4337,13 @@
       <c r="I45" s="33">
         <v>1</v>
       </c>
-      <c r="J45" s="83"/>
+      <c r="J45" s="84"/>
       <c r="K45" s="32">
         <f t="shared" ref="K45:K46" si="1">I45*E45</f>
         <v>8.09</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
         <v>291</v>
       </c>
@@ -4370,13 +4371,13 @@
       <c r="I46" s="33">
         <v>1</v>
       </c>
-      <c r="J46" s="83"/>
+      <c r="J46" s="84"/>
       <c r="K46" s="32">
         <f t="shared" si="1"/>
         <v>9.99</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="54"/>
       <c r="B47" s="54"/>
       <c r="C47" s="55"/>
@@ -4386,10 +4387,10 @@
       <c r="G47" s="54"/>
       <c r="H47" s="54"/>
       <c r="I47" s="54"/>
-      <c r="J47" s="82"/>
+      <c r="J47" s="83"/>
       <c r="K47" s="56"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="47" t="s">
         <v>292</v>
       </c>
@@ -4415,13 +4416,13 @@
         <v>259</v>
       </c>
       <c r="I48" s="33"/>
-      <c r="J48" s="83"/>
+      <c r="J48" s="84"/>
       <c r="K48" s="32">
         <f t="shared" ref="K48:K55" si="2">I48*E48</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
         <v>293</v>
       </c>
@@ -4447,13 +4448,13 @@
         <v>259</v>
       </c>
       <c r="I49" s="33"/>
-      <c r="J49" s="83"/>
+      <c r="J49" s="84"/>
       <c r="K49" s="32">
         <f>I49*E49</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59"/>
       <c r="B50" s="54"/>
       <c r="C50" s="55"/>
@@ -4463,10 +4464,10 @@
       <c r="G50" s="54"/>
       <c r="H50" s="54"/>
       <c r="I50" s="54"/>
-      <c r="J50" s="82"/>
+      <c r="J50" s="83"/>
       <c r="K50" s="56"/>
     </row>
-    <row r="51" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="47" t="s">
         <v>294</v>
       </c>
@@ -4494,14 +4495,14 @@
       <c r="I51" s="33">
         <v>3</v>
       </c>
-      <c r="J51" s="83"/>
+      <c r="J51" s="84"/>
       <c r="K51" s="32">
         <f t="shared" ref="K51:K52" si="3">I51*E51</f>
         <v>23.37</v>
       </c>
       <c r="Q51" s="31"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
         <v>295</v>
       </c>
@@ -4514,26 +4515,26 @@
       <c r="D52" s="33">
         <v>9</v>
       </c>
-      <c r="E52" s="69">
+      <c r="E52" s="70">
         <v>22.99</v>
       </c>
       <c r="F52" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="G52" s="85" t="s">
+      <c r="G52" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="87" t="s">
+      <c r="H52" s="88" t="s">
         <v>259</v>
       </c>
-      <c r="I52" s="89"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="69">
+      <c r="I52" s="90"/>
+      <c r="J52" s="84"/>
+      <c r="K52" s="70">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="47" t="s">
         <v>296</v>
       </c>
@@ -4546,17 +4547,17 @@
       <c r="D53" s="33">
         <v>7</v>
       </c>
-      <c r="E53" s="70"/>
+      <c r="E53" s="71"/>
       <c r="F53" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="G53" s="86"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="90"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="70"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G53" s="87"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="91"/>
+      <c r="J53" s="84"/>
+      <c r="K53" s="71"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="47" t="s">
         <v>297</v>
       </c>
@@ -4584,13 +4585,13 @@
       <c r="I54" s="33">
         <v>1</v>
       </c>
-      <c r="J54" s="83"/>
+      <c r="J54" s="84"/>
       <c r="K54" s="32">
         <f>I54*E54</f>
         <v>9.99</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
         <v>298</v>
       </c>
@@ -4616,13 +4617,13 @@
         <v>258</v>
       </c>
       <c r="I55" s="47"/>
-      <c r="J55" s="83"/>
+      <c r="J55" s="84"/>
       <c r="K55" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="47" t="s">
         <v>299</v>
       </c>
@@ -4648,10 +4649,10 @@
         <v>248</v>
       </c>
       <c r="I56" s="33"/>
-      <c r="J56" s="84"/>
+      <c r="J56" s="85"/>
       <c r="K56" s="32"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="54"/>
       <c r="B57" s="54"/>
       <c r="C57" s="55"/>
@@ -4664,7 +4665,7 @@
       <c r="J57" s="56"/>
       <c r="K57" s="56"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="47" t="s">
         <v>300</v>
       </c>
@@ -4678,16 +4679,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="32"/>
-      <c r="F58" s="80" t="s">
+      <c r="F58" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="G58" s="72"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="72"/>
-      <c r="J58" s="72"/>
-      <c r="K58" s="73"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G58" s="73"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="73"/>
+      <c r="K58" s="74"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="47" t="s">
         <v>301</v>
       </c>
@@ -4701,14 +4702,14 @@
         <v>1</v>
       </c>
       <c r="E59" s="32"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="75"/>
-      <c r="H59" s="75"/>
-      <c r="I59" s="75"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="76"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F59" s="75"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76"/>
+      <c r="J59" s="76"/>
+      <c r="K59" s="77"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="47" t="s">
         <v>302</v>
       </c>
@@ -4722,14 +4723,14 @@
         <v>44</v>
       </c>
       <c r="E60" s="32"/>
-      <c r="F60" s="74"/>
-      <c r="G60" s="75"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="75"/>
-      <c r="J60" s="75"/>
-      <c r="K60" s="76"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F60" s="75"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="77"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
         <v>303</v>
       </c>
@@ -4743,14 +4744,14 @@
         <v>22</v>
       </c>
       <c r="E61" s="32"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="75"/>
-      <c r="J61" s="75"/>
-      <c r="K61" s="76"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F61" s="75"/>
+      <c r="G61" s="76"/>
+      <c r="H61" s="76"/>
+      <c r="I61" s="76"/>
+      <c r="J61" s="76"/>
+      <c r="K61" s="77"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="47" t="s">
         <v>304</v>
       </c>
@@ -4764,14 +4765,14 @@
         <v>2</v>
       </c>
       <c r="E62" s="32"/>
-      <c r="F62" s="74"/>
-      <c r="G62" s="75"/>
-      <c r="H62" s="75"/>
-      <c r="I62" s="75"/>
-      <c r="J62" s="75"/>
-      <c r="K62" s="76"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F62" s="75"/>
+      <c r="G62" s="76"/>
+      <c r="H62" s="76"/>
+      <c r="I62" s="76"/>
+      <c r="J62" s="76"/>
+      <c r="K62" s="77"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
         <v>305</v>
       </c>
@@ -4785,14 +4786,14 @@
         <v>2</v>
       </c>
       <c r="E63" s="32"/>
-      <c r="F63" s="74"/>
-      <c r="G63" s="75"/>
-      <c r="H63" s="75"/>
-      <c r="I63" s="75"/>
-      <c r="J63" s="75"/>
-      <c r="K63" s="76"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F63" s="75"/>
+      <c r="G63" s="76"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="76"/>
+      <c r="J63" s="76"/>
+      <c r="K63" s="77"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="47" t="s">
         <v>306</v>
       </c>
@@ -4806,14 +4807,14 @@
         <v>1</v>
       </c>
       <c r="E64" s="32"/>
-      <c r="F64" s="74"/>
-      <c r="G64" s="75"/>
-      <c r="H64" s="75"/>
-      <c r="I64" s="75"/>
-      <c r="J64" s="75"/>
-      <c r="K64" s="76"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F64" s="75"/>
+      <c r="G64" s="76"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
+      <c r="J64" s="76"/>
+      <c r="K64" s="77"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="47" t="s">
         <v>307</v>
       </c>
@@ -4827,14 +4828,14 @@
         <v>1</v>
       </c>
       <c r="E65" s="32"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="75"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="75"/>
-      <c r="J65" s="75"/>
-      <c r="K65" s="76"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F65" s="75"/>
+      <c r="G65" s="76"/>
+      <c r="H65" s="76"/>
+      <c r="I65" s="76"/>
+      <c r="J65" s="76"/>
+      <c r="K65" s="77"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="47" t="s">
         <v>308</v>
       </c>
@@ -4848,14 +4849,14 @@
         <v>1</v>
       </c>
       <c r="E66" s="32"/>
-      <c r="F66" s="74"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="75"/>
-      <c r="I66" s="75"/>
-      <c r="J66" s="75"/>
-      <c r="K66" s="76"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F66" s="75"/>
+      <c r="G66" s="76"/>
+      <c r="H66" s="76"/>
+      <c r="I66" s="76"/>
+      <c r="J66" s="76"/>
+      <c r="K66" s="77"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="47" t="s">
         <v>309</v>
       </c>
@@ -4869,14 +4870,14 @@
         <v>1</v>
       </c>
       <c r="E67" s="32"/>
-      <c r="F67" s="74"/>
-      <c r="G67" s="75"/>
-      <c r="H67" s="75"/>
-      <c r="I67" s="75"/>
-      <c r="J67" s="75"/>
-      <c r="K67" s="76"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F67" s="75"/>
+      <c r="G67" s="76"/>
+      <c r="H67" s="76"/>
+      <c r="I67" s="76"/>
+      <c r="J67" s="76"/>
+      <c r="K67" s="77"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="47" t="s">
         <v>310</v>
       </c>
@@ -4890,14 +4891,14 @@
         <v>1</v>
       </c>
       <c r="E68" s="32"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="75"/>
-      <c r="J68" s="75"/>
-      <c r="K68" s="76"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F68" s="75"/>
+      <c r="G68" s="76"/>
+      <c r="H68" s="76"/>
+      <c r="I68" s="76"/>
+      <c r="J68" s="76"/>
+      <c r="K68" s="77"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="47" t="s">
         <v>311</v>
       </c>
@@ -4911,14 +4912,14 @@
         <v>1</v>
       </c>
       <c r="E69" s="32"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="75"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="75"/>
-      <c r="J69" s="75"/>
-      <c r="K69" s="76"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F69" s="75"/>
+      <c r="G69" s="76"/>
+      <c r="H69" s="76"/>
+      <c r="I69" s="76"/>
+      <c r="J69" s="76"/>
+      <c r="K69" s="77"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="47" t="s">
         <v>312</v>
       </c>
@@ -4932,14 +4933,14 @@
         <v>1</v>
       </c>
       <c r="E70" s="32"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="75"/>
-      <c r="K70" s="76"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F70" s="75"/>
+      <c r="G70" s="76"/>
+      <c r="H70" s="76"/>
+      <c r="I70" s="76"/>
+      <c r="J70" s="76"/>
+      <c r="K70" s="77"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="47" t="s">
         <v>312</v>
       </c>
@@ -4954,7 +4955,7 @@
       </c>
       <c r="E71" s="32"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="36">
         <v>1.4</v>
       </c>
@@ -4978,7 +4979,7 @@
         <v>60.139999999999993</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="47" t="s">
         <v>184</v>
       </c>
@@ -5012,7 +5013,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="54"/>
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
@@ -5025,7 +5026,7 @@
       <c r="J75" s="67"/>
       <c r="K75" s="56"/>
     </row>
-    <row r="76" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="47" t="s">
         <v>182</v>
       </c>
@@ -5057,7 +5058,7 @@
         <v>38.97</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="47" t="s">
         <v>179</v>
       </c>
@@ -5089,7 +5090,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="47"/>
       <c r="B78" s="33"/>
       <c r="C78" s="34"/>
@@ -5105,7 +5106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="E22:E23"/>
